--- a/2. Báo cáo - giấy tờ/2. Bảo hành/Xuất nhập kho 2026/Xuất kho/Tháng 07/XKBH_BaoHanhVNET_060726.xlsx
+++ b/2. Báo cáo - giấy tờ/2. Bảo hành/Xuất nhập kho 2026/Xuất kho/Tháng 07/XKBH_BaoHanhVNET_060726.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\2. Bảo hành\Xuất nhập kho 2026\Xuất kho\Tháng 07\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A87B0325-0B10-463A-B44D-AB1F941B9699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5DD56DF-03B8-4255-A9DD-2AA2B8EFE692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -507,6 +507,30 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -575,30 +599,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1027,66 +1027,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="38" t="s">
+      <c r="B1" s="38"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="40"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="48"/>
     </row>
     <row r="2" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="32"/>
-      <c r="B2" s="33"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="41" t="s">
+      <c r="A2" s="40"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="42"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="50"/>
     </row>
     <row r="3" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="32"/>
-      <c r="B3" s="33"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="41" t="s">
+      <c r="A3" s="40"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="42"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="50"/>
     </row>
     <row r="4" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="35"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="43" t="s">
+      <c r="A4" s="43"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="44"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="52"/>
     </row>
     <row r="5" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="28"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="36"/>
     </row>
     <row r="6" spans="1:8" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
@@ -1153,123 +1153,123 @@
       </c>
     </row>
     <row r="10" spans="1:8" s="23" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="51">
+      <c r="A10" s="26">
         <v>1</v>
       </c>
-      <c r="B10" s="52" t="s">
+      <c r="B10" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="50" t="s">
+      <c r="C10" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="55">
+      <c r="D10" s="30">
         <v>30</v>
       </c>
-      <c r="E10" s="51"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="45" t="s">
+      <c r="E10" s="26"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="H10" s="50"/>
+      <c r="H10" s="25"/>
     </row>
     <row r="11" spans="1:8" s="23" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="51">
+      <c r="A11" s="26">
         <v>2</v>
       </c>
-      <c r="B11" s="52" t="s">
+      <c r="B11" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="50" t="s">
+      <c r="C11" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="55">
+      <c r="D11" s="30">
         <v>50</v>
       </c>
-      <c r="E11" s="51"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="50"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="25"/>
     </row>
     <row r="12" spans="1:8" s="23" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="51">
+      <c r="A12" s="26">
         <v>3</v>
       </c>
-      <c r="B12" s="52" t="s">
+      <c r="B12" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="50" t="s">
+      <c r="C12" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="55">
+      <c r="D12" s="30">
         <v>50</v>
       </c>
-      <c r="E12" s="51"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="50"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="25"/>
     </row>
     <row r="13" spans="1:8" s="23" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="51">
+      <c r="A13" s="26">
         <v>4</v>
       </c>
-      <c r="B13" s="52" t="s">
+      <c r="B13" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="50" t="s">
+      <c r="C13" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="55">
+      <c r="D13" s="30">
         <v>50</v>
       </c>
-      <c r="E13" s="51"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="50"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="25"/>
     </row>
     <row r="14" spans="1:8" s="23" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="51">
+      <c r="A14" s="26">
         <v>5</v>
       </c>
-      <c r="B14" s="52" t="s">
+      <c r="B14" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="50" t="s">
+      <c r="C14" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="55">
+      <c r="D14" s="30">
         <v>50</v>
       </c>
-      <c r="E14" s="51"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="50"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="25"/>
     </row>
     <row r="15" spans="1:8" s="23" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="51">
+      <c r="A15" s="26">
         <v>6</v>
       </c>
-      <c r="B15" s="52" t="s">
+      <c r="B15" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="50" t="s">
+      <c r="C15" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="55">
+      <c r="D15" s="30">
         <v>50</v>
       </c>
-      <c r="E15" s="53"/>
-      <c r="F15" s="54"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="50"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="55"/>
+      <c r="H15" s="25"/>
     </row>
     <row r="16" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="25" t="s">
+      <c r="A16" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="25"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
       <c r="F16" s="20">
         <f>SUM(F15)</f>
         <v>0</v>
@@ -1288,37 +1288,37 @@
       <c r="H17" s="3"/>
     </row>
     <row r="18" spans="1:8" s="2" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="48" t="s">
+      <c r="A18" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="48"/>
-      <c r="C18" s="48" t="s">
+      <c r="B18" s="31"/>
+      <c r="C18" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="48"/>
-      <c r="E18" s="48"/>
-      <c r="F18" s="48" t="s">
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="G18" s="48"/>
+      <c r="G18" s="31"/>
       <c r="H18" s="21" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="49" t="s">
+      <c r="A19" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="B19" s="49"/>
-      <c r="C19" s="49" t="s">
+      <c r="B19" s="32"/>
+      <c r="C19" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="D19" s="49"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="49" t="s">
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="G19" s="49"/>
+      <c r="G19" s="32"/>
       <c r="H19" s="22" t="s">
         <v>3</v>
       </c>
@@ -1369,19 +1369,19 @@
       <c r="H24" s="21"/>
     </row>
     <row r="25" spans="1:8" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="48" t="s">
+      <c r="A25" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="B25" s="48"/>
-      <c r="C25" s="48" t="s">
+      <c r="B25" s="31"/>
+      <c r="C25" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="D25" s="48"/>
-      <c r="E25" s="48"/>
-      <c r="F25" s="48" t="s">
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="G25" s="48"/>
+      <c r="G25" s="31"/>
       <c r="H25" s="21" t="s">
         <v>25</v>
       </c>
@@ -1410,6 +1410,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="G10:G15"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="A19:B19"/>
@@ -1419,14 +1427,6 @@
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="C25:E25"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D4:H4"/>
-    <mergeCell ref="G10:G15"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
